--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104692_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104692_W26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9617</v>
+        <v>1.392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5438</v>
+        <v>-0.1794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4179</v>
+        <v>1.5713</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8231000000000001</v>
+        <v>0.0007</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2176</v>
+        <v>0.4309</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3945</v>
+        <v>-0.4302</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4856</v>
+        <v>-0.0024</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0745</v>
+        <v>0.6755</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5889</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3375</v>
+        <v>0.0032</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1431</v>
+        <v>-0.2446</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1945</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6221</v>
+        <v>0.5702</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7229</v>
+        <v>0.506</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1007</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4822</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1212</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8633</v>
+        <v>1.1479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2934</v>
+        <v>-0.2163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5699</v>
+        <v>1.3641</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3363</v>
+        <v>-2.9177</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1631</v>
+        <v>-1.8751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733</v>
+        <v>-1.0426</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4427</v>
+        <v>-2.1156</v>
       </c>
       <c r="K3" t="n">
-        <v>1.368</v>
+        <v>-0.6108</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>-1.5048</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1063</v>
+        <v>-0.8022</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.205</v>
+        <v>-1.2643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.4622</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2075</v>
+        <v>-0.4776</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4386</v>
+        <v>0.0877</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2311</v>
+        <v>-0.5653</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3553</v>
+        <v>1.0743</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3468</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7021</v>
+        <v>0.2351</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0042</v>
+        <v>-0.8424</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4329</v>
+        <v>-1.2341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4371</v>
+        <v>0.3916</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0112</v>
+        <v>-0.5313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6856</v>
+        <v>-1.1041</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6744</v>
+        <v>0.5728</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0153</v>
+        <v>-0.3111</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2526</v>
+        <v>-0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2373</v>
+        <v>-0.1811</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4552</v>
+        <v>0.7605</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6775</v>
+        <v>1.0841</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2223</v>
+        <v>-0.3235</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>0.4733</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1075</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1428</v>
+        <v>0.6325</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3515</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2087</v>
+        <v>0.7039</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7591</v>
+        <v>1.3364</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6206</v>
+        <v>1.1605</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1386</v>
+        <v>0.1759</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2607</v>
+        <v>1.4362</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1039</v>
+        <v>1.3617</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1568</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0198</v>
+        <v>-0.0998</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7245</v>
+        <v>-0.2012</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2954</v>
+        <v>0.1014</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0054</v>
+        <v>-0.021</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0907</v>
+        <v>0.0858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1067</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1413</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1474</v>
+        <v>-0.2784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006</v>
+        <v>0.2384</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.522</v>
+        <v>-0.4547</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1627</v>
+        <v>0.2129</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3593</v>
+        <v>-0.6676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0764</v>
+        <v>-0.4567</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0355</v>
+        <v>0.989</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>-1.4457</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5984</v>
+        <v>0.0019</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1272</v>
+        <v>-0.7761</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4712</v>
+        <v>0.778</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.434</v>
+        <v>-0.9315</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7743</v>
+        <v>0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2083</v>
+        <v>-0.952</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7712</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3485</v>
+        <v>-0.378</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.43</v>
+        <v>0.8766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08160000000000001</v>
+        <v>-1.2546</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4417</v>
+        <v>-0.7472</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2194</v>
+        <v>-0.6149</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6611</v>
+        <v>-0.1323</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4214</v>
+        <v>1.2578</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0075</v>
+        <v>0.1034</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4289</v>
+        <v>1.1543</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0203</v>
+        <v>-2.005</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.788</v>
+        <v>-0.7184</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7678</v>
+        <v>-1.2866</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2412</v>
+        <v>-0.5413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1693</v>
+        <v>-0.3812</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0719</v>
+        <v>-0.1601</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.373</v>
+        <v>-0.5091</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.429</v>
+        <v>-0.7024</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0559</v>
+        <v>0.1933</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9134</v>
+        <v>-1.5299</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8685</v>
+        <v>-0.1854</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0449</v>
+        <v>-1.3445</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0908</v>
+        <v>0.0418</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5928</v>
+        <v>-0.0699</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4981</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8225</v>
+        <v>-1.5717</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2758</v>
+        <v>-0.1155</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4532</v>
+        <v>-1.4562</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0079</v>
+        <v>-0.8002</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1644</v>
+        <v>0.2574</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8435</v>
+        <v>-1.0576</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5068</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.07</v>
+        <v>-1.0449</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9786</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0914</v>
+        <v>-0.1805</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9676</v>
+        <v>-0.9696</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2852</v>
+        <v>0.3101</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2852</v>
+        <v>0.1917</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6257</v>
+        <v>-3.0566</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4654</v>
+        <v>-1.0807</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0912</v>
+        <v>-1.9759</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7029</v>
+        <v>-2.7088</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9002</v>
+        <v>-2.9117</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0025</v>
+        <v>-2.0209</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0025</v>
+        <v>-2.0209</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7003</v>
+        <v>-0.6879</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1283</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>2.468</v>
+        <v>0.9403</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3396</v>
+        <v>-0.2473</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2787</v>
+        <v>-5.5359</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9676</v>
+        <v>-2.4046</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3111</v>
+        <v>-3.1313</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9726</v>
+        <v>-4.4521</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2192</v>
+        <v>-0.3098</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7534</v>
+        <v>-4.1423</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7401</v>
+        <v>-2.2647</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7579</v>
+        <v>-0.0075</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4981</v>
+        <v>-2.2572</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2325</v>
+        <v>-2.1874</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9771</v>
+        <v>-0.3023</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2554</v>
+        <v>-1.8851</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6009</v>
+        <v>-1.1812</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4265</v>
+        <v>0.0877</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0274</v>
+        <v>-1.2689</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4783</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>M. HEIDEGGER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8215</v>
+        <v>-5.6457</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6814</v>
+        <v>-4.0434</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1401</v>
+        <v>-1.6023</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4531</v>
+        <v>-1.7937</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3029</v>
+        <v>-0.2902</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.1502</v>
+        <v>-1.5035</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2338</v>
+        <v>-0.0757</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0133</v>
+        <v>0.1411</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>-0.2169</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2193</v>
+        <v>-1.718</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3162</v>
+        <v>-0.4314</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.903</v>
+        <v>-1.2866</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2683</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4514</v>
+        <v>-0.7853</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2208</v>
+        <v>-0.3256</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2307</v>
+        <v>-0.4596</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-1.018</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. HEIDEGGER</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9857</v>
+        <v>-6.0167</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4764</v>
+        <v>-3.644</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5092</v>
+        <v>-2.3728</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7857</v>
+        <v>-2.9758</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.293</v>
+        <v>-0.2292</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4928</v>
+        <v>-2.7465</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0487</v>
+        <v>-0.7711</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1487</v>
+        <v>0.7337</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1974</v>
+        <v>-1.5048</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7371</v>
+        <v>-2.2047</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4417</v>
+        <v>-0.9629</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2954</v>
+        <v>-1.2417</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0415</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1299</v>
+        <v>-1.3369</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7984</v>
+        <v>-0.2096</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3315</v>
+        <v>-1.1273</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0285</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0285</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.3213</v>
+        <v>-17.9802</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.8031</v>
+        <v>-11.7692</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.5183</v>
+        <v>-6.2113</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.0091</v>
+        <v>-18.0548</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7347</v>
+        <v>-5.811599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.2746</v>
+        <v>-12.2433</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.9836</v>
+        <v>-6.2578</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4142000000000004</v>
+        <v>0.2256999999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.398099999999999</v>
+        <v>-6.483599999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.0252</v>
+        <v>-11.7971</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.1488</v>
+        <v>-6.0374</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.876600000000001</v>
+        <v>-5.7596</v>
       </c>
       <c r="P14" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3415</v>
+        <v>-11.3815</v>
       </c>
       <c r="R14" t="n">
-        <v>20.415</v>
+        <v>20.4868</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.082800000000001</v>
+        <v>-3.7412</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8906</v>
+        <v>2.2715</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.9734</v>
+        <v>-6.0124</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.302499999999999</v>
+        <v>-5.289400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6319</v>
+        <v>3.5989</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.934399999999998</v>
+        <v>-8.888400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8072</v>
+        <v>5.8597</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8735</v>
+        <v>3.9575</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9337</v>
+        <v>1.9023</v>
       </c>
       <c r="G15" t="n">
-        <v>5.6169</v>
+        <v>5.6316</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9016</v>
+        <v>0.9154</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7153</v>
+        <v>4.7162</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1341</v>
+        <v>3.1201</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9853</v>
+        <v>2.9789</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4829</v>
+        <v>2.5115</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7529</v>
+        <v>0.7743</v>
       </c>
       <c r="O15" t="n">
-        <v>1.73</v>
+        <v>1.7372</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1805</v>
+        <v>0.236</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3176</v>
+        <v>0.4387</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.137</v>
+        <v>-0.2026</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2029</v>
+        <v>5.2095</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3723</v>
+        <v>3.0291</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8306</v>
+        <v>2.1805</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2524</v>
+        <v>1.5685</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1223</v>
+        <v>-1.0034</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1301</v>
+        <v>2.572</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5745</v>
+        <v>2.3559</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2122</v>
+        <v>0.1896</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3623</v>
+        <v>2.1663</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6779</v>
+        <v>-0.7874</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9102</v>
+        <v>-1.1931</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7678</v>
+        <v>0.4057</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0495</v>
+        <v>1.3647</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0907</v>
+        <v>0.6731</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1402</v>
+        <v>0.6915</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0249</v>
+        <v>4.8337</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6343</v>
+        <v>2.3434</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3905</v>
+        <v>2.4903</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5621</v>
+        <v>3.2585</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0234</v>
+        <v>2.1388</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5855</v>
+        <v>1.1197</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3813</v>
+        <v>1.5483</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1905</v>
+        <v>1.2066</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1909</v>
+        <v>0.3417</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8193</v>
+        <v>1.7103</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2139</v>
+        <v>0.9322</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3946</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1945</v>
+        <v>-0.4248</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.747</v>
+        <v>0.0926</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9415</v>
+        <v>-0.5174</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3308</v>
+        <v>3.6548</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7961</v>
+        <v>3.3361</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5347</v>
+        <v>0.3188</v>
       </c>
       <c r="G18" t="n">
-        <v>3.173</v>
+        <v>3.1518</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8758</v>
+        <v>-0.8814</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0488</v>
+        <v>4.0332</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6542</v>
+        <v>3.6104</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1172</v>
+        <v>0.0959</v>
       </c>
       <c r="L18" t="n">
-        <v>3.537</v>
+        <v>3.5145</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4812</v>
+        <v>-0.4587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2258</v>
+        <v>1.5714</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3176</v>
+        <v>0.9125</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9082</v>
+        <v>0.6589</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9762</v>
+        <v>2.8949</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4033</v>
+        <v>1.1446</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5729</v>
+        <v>1.7503</v>
       </c>
       <c r="G19" t="n">
-        <v>3.0918</v>
+        <v>3.0977</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0705</v>
+        <v>3.0784</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0213</v>
+        <v>0.0193</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0758</v>
+        <v>1.0587</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M19" t="n">
-        <v>2.016</v>
+        <v>2.039</v>
       </c>
       <c r="N19" t="n">
-        <v>1.131</v>
+        <v>1.1479</v>
       </c>
       <c r="O19" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0741</v>
+        <v>-0.1542</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4431</v>
+        <v>-0.2887</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6678</v>
+        <v>2.0177</v>
       </c>
       <c r="E20" t="n">
-        <v>1.935</v>
+        <v>0.9806</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7327</v>
+        <v>1.0371</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3477</v>
+        <v>0.3531</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4863</v>
+        <v>0.4854</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1386</v>
+        <v>-0.1323</v>
       </c>
       <c r="J20" t="n">
-        <v>0.619</v>
+        <v>0.6093</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2712</v>
+        <v>-0.2562</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8003</v>
+        <v>0.1394</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1553</v>
+        <v>0.2135</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3551</v>
+        <v>-0.0741</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.554</v>
+        <v>1.2106</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06</v>
+        <v>-0.7783</v>
       </c>
       <c r="F21" t="n">
-        <v>2.614</v>
+        <v>1.9889</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1562</v>
+        <v>1.8801</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5556</v>
+        <v>1.7312</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7117</v>
+        <v>0.1489</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0345</v>
+        <v>-0.5168</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4533</v>
+        <v>0.9136</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4878</v>
+        <v>-1.4303</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1906</v>
+        <v>2.3969</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0089</v>
+        <v>0.8176</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1995</v>
+        <v>1.5793</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.7635</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.6708</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5.1367</v>
+        <v>-0.3053</v>
       </c>
       <c r="T21" t="n">
-        <v>4.2312</v>
+        <v>0.3319</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9055</v>
+        <v>-0.6372</v>
       </c>
       <c r="V21" t="n">
-        <v>2.0246</v>
+        <v>0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4141</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6105</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1597</v>
+        <v>1.1943</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2644</v>
+        <v>0.1798</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4241</v>
+        <v>1.0145</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0161</v>
+        <v>0.0166</v>
       </c>
       <c r="H22" t="n">
-        <v>0.264</v>
+        <v>0.2669</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2479</v>
+        <v>-0.2504</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6814</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6653</v>
+        <v>-0.6442</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1851</v>
+        <v>1.2264</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2299</v>
+        <v>0.7058</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0448</v>
+        <v>0.5206</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0151</v>
+        <v>0.34</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3536</v>
+        <v>-2.3407</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3385</v>
+        <v>2.6806</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8676</v>
+        <v>0.1608</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7184</v>
+        <v>-0.5544</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1493</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5057</v>
+        <v>-0.0543</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.4374</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4234</v>
+        <v>-0.4917</v>
       </c>
       <c r="M23" t="n">
-        <v>2.3733</v>
+        <v>0.2151</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8006</v>
+        <v>-0.9918</v>
       </c>
       <c r="O23" t="n">
-        <v>1.5727</v>
+        <v>1.2069</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-5.6908</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5198</v>
+        <v>2.9382</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2601</v>
+        <v>1.9995</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2597</v>
+        <v>0.9388</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7712</v>
+        <v>2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>1.405</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2249</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1595</v>
+        <v>-0.547</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0718</v>
+        <v>-1.0786</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0877</v>
+        <v>0.5316</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4603</v>
+        <v>-0.5455</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1645</v>
+        <v>0.7924</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2958</v>
+        <v>-1.3379</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6696</v>
+        <v>0.4423</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7069</v>
+        <v>1.3962</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0373</v>
+        <v>-0.9539</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9877</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4576</v>
+        <v>-0.6037</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3331</v>
+        <v>-0.384</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4842</v>
+        <v>-0.2276</v>
       </c>
       <c r="T24" t="n">
-        <v>0.369</v>
+        <v>-0.1535</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1152</v>
+        <v>-0.0741</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3176</v>
+        <v>-0.2292</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.2292</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.2974</v>
+        <v>-0.9035</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5235</v>
+        <v>-0.9643</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2261</v>
+        <v>0.0608</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.545</v>
+        <v>-1.4535</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7877999999999999</v>
+        <v>-1.1633</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3328</v>
+        <v>-0.2902</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4616</v>
+        <v>-0.6802</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4027</v>
+        <v>-0.7174</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9409999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0066</v>
+        <v>-0.7733</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6149</v>
+        <v>-0.4458</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>-0.3275</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9811</v>
+        <v>0.7305</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6261</v>
+        <v>0.4899</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3551</v>
+        <v>0.2407</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2249</v>
+        <v>-1.3187</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.2249</v>
+        <v>-0.7739</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9302</v>
+        <v>-5.0669</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.2231</v>
+        <v>-3.5979</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7071</v>
+        <v>-1.469</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9305</v>
+        <v>0.9352</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9276</v>
+        <v>0.9296</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3469</v>
+        <v>-0.3574</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.0186</v>
+        <v>-1.0277</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2773</v>
+        <v>1.2926</v>
       </c>
       <c r="N26" t="n">
-        <v>1.0214</v>
+        <v>1.0333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4996</v>
+        <v>-0.6363</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5263</v>
+        <v>0.174</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0259</v>
+        <v>-0.8104</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>18.3213</v>
+        <v>20.6978</v>
       </c>
       <c r="E27" t="n">
-        <v>6.5181</v>
+        <v>6.2113</v>
       </c>
       <c r="F27" t="n">
-        <v>11.803</v>
+        <v>14.4867</v>
       </c>
       <c r="G27" t="n">
-        <v>18.009</v>
+        <v>18.0549</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7344</v>
+        <v>5.811599999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>12.2745</v>
+        <v>12.2433</v>
       </c>
       <c r="J27" t="n">
-        <v>12.0252</v>
+        <v>11.7971</v>
       </c>
       <c r="K27" t="n">
-        <v>6.1488</v>
+        <v>6.037500000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>5.8766</v>
+        <v>5.759600000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>5.983600000000001</v>
+        <v>6.257899999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.4142999999999999</v>
+        <v>-0.2257000000000002</v>
       </c>
       <c r="O27" t="n">
-        <v>6.3979</v>
+        <v>6.483599999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.1053</v>
       </c>
       <c r="Q27" t="n">
-        <v>-20.415</v>
+        <v>-20.487</v>
       </c>
       <c r="R27" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S27" t="n">
-        <v>4.083000000000001</v>
+        <v>6.4584</v>
       </c>
       <c r="T27" t="n">
-        <v>5.9734</v>
+        <v>6.0125</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8905</v>
+        <v>0.4459999999999997</v>
       </c>
       <c r="V27" t="n">
-        <v>5.3027</v>
+        <v>5.2897</v>
       </c>
       <c r="W27" t="n">
-        <v>8.9345</v>
+        <v>8.888599999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.6318</v>
+        <v>-3.5987</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104692_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104692_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.888400000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104692_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-3.5987</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
